--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012DD679-476A-425C-AACE-BBD28B67A3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397726F5-284A-4318-85E7-8D3E36E940C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1001" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -98,6 +98,14 @@
   </si>
   <si>
     <t>GameAI_XunLuo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AIConfigId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -105,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +154,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -176,7 +191,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,6 +202,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -467,7 +483,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="9.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.90625" style="1" customWidth="1"/>
@@ -483,8 +499,8 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="C1" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>3</v>
@@ -507,8 +523,8 @@
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
+      <c r="C2" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>8</v>
@@ -596,7 +612,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="9.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.6328125" style="1" customWidth="1"/>

--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{397726F5-284A-4318-85E7-8D3E36E940C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EC050D-8FF8-4195-A8E2-97E6B61D7C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,15 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>AIConfigId</t>
   </si>
   <si>
     <t>Order</t>
@@ -105,7 +102,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
+    <t>int#ref=DTUnitConfig</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -500,66 +497,66 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -575,10 +572,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -594,10 +591,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -628,68 +625,68 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -705,10 +702,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
@@ -724,10 +721,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EC050D-8FF8-4195-A8E2-97E6B61D7C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B462773-0D88-4818-AA5D-B097911C20FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1001" sheetId="6" r:id="rId1"/>
-    <sheet name="2001" sheetId="7" r:id="rId2"/>
+    <sheet name="1001" sheetId="1" r:id="rId1"/>
+    <sheet name="2001" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -42,6 +42,9 @@
     <t>Id</t>
   </si>
   <si>
+    <t>AIConfigId</t>
+  </si>
+  <si>
     <t>Order</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>int#ref=DTUnitConfig</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -82,27 +88,41 @@
   </si>
   <si>
     <t>节点参数</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>巡逻</t>
   </si>
   <si>
     <t>GameAI_Attack</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>攻击</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>GameAI_XunLuo</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>AIConfigId</t>
+    <t>巡逻</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>int#ref=DTUnitConfig</t>
+    <t>2,4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameAI_Idle</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>待机</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -110,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,6 +178,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -188,7 +216,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -198,12 +226,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -476,125 +515,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.90625" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.36328125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>20</v>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4"/>
-      <c r="B4" s="4">
-        <f>C4*100+D4</f>
+      <c r="B4" s="6">
         <v>100101</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>1001</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="F4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4"/>
-      <c r="B5" s="4">
-        <f>C5*100+D5</f>
+      <c r="B5" s="6">
         <v>100102</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>1001</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="6">
         <v>2</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
+      <c r="E5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="10">
+        <v>100103</v>
+      </c>
+      <c r="C6" s="10">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -605,130 +669,156 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.6328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.453125" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.36328125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>20</v>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>21</v>
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4"/>
-      <c r="B4" s="4">
-        <f>C4*100+D4</f>
+      <c r="B4" s="6">
         <v>200101</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>2001</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="F4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4"/>
-      <c r="B5" s="4">
-        <f>C5*100+D5</f>
+      <c r="B5" s="6">
         <v>200102</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>2001</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="6">
         <v>2</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
+      <c r="E5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="10">
+        <v>200103</v>
+      </c>
+      <c r="C6" s="10">
+        <v>2001</v>
+      </c>
+      <c r="D6" s="10">
+        <v>3</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B462773-0D88-4818-AA5D-B097911C20FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501413A5-8F1A-4B3D-9D57-A78A8A69088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1001" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -95,18 +95,6 @@
   </si>
   <si>
     <t>攻击</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>GameAI_XunLuo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>巡逻</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -515,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1" customWidth="1"/>
@@ -617,48 +605,27 @@
         <v>19</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6">
-        <v>100102</v>
-      </c>
-      <c r="C5" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="10">
+        <v>100103</v>
+      </c>
+      <c r="C5" s="10">
         <v>1001</v>
       </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="10">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="10">
-        <v>100103</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1001</v>
-      </c>
-      <c r="D6" s="10">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -669,12 +636,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" style="1" customWidth="1"/>
     <col min="5" max="5" width="28.90625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.6328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.453125" style="1" customWidth="1"/>
@@ -772,48 +739,27 @@
         <v>19</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6">
-        <v>200102</v>
-      </c>
-      <c r="C5" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="10">
+        <v>200103</v>
+      </c>
+      <c r="C5" s="10">
         <v>2001</v>
       </c>
-      <c r="D5" s="6">
-        <v>2</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="D5" s="10">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="10">
-        <v>200103</v>
-      </c>
-      <c r="C6" s="10">
-        <v>2001</v>
-      </c>
-      <c r="D6" s="10">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501413A5-8F1A-4B3D-9D57-A78A8A69088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAE4879-2889-45CF-AE56-6B5864E8EA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.90625" style="1" customWidth="1"/>

--- a/Design/Excel/ET/Datas/Game/GameAI.xlsx
+++ b/Design/Excel/ET/Datas/Game/GameAI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAE4879-2889-45CF-AE56-6B5864E8EA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0D47D9-6856-4FEB-9298-8481A7585B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" tabRatio="809" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1001" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -103,10 +103,6 @@
   </si>
   <si>
     <t>待机</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -130,18 +126,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -605,7 +604,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -624,9 +623,7 @@
       <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="G5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -739,7 +736,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -758,9 +755,7 @@
       <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="G5" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
